--- a/05-项目管理/02-进度管理/02-里程碑追踪表.xlsx
+++ b/05-项目管理/02-进度管理/02-里程碑追踪表.xlsx
@@ -91,7 +91,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -118,11 +118,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,6 +152,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +536,13 @@
           <t>02-里程碑追踪表</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -534,6 +550,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -541,6 +558,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -548,6 +566,9 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -555,6 +576,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -562,6 +584,9 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -569,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -576,6 +602,9 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -583,6 +612,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -590,27 +620,29 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M01 项目启动——项目章程签署、团队组建完成</t>
+          <t xml:space="preserve">  *  某型号 项目启动——项目章程签署、团队组建完成</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M02 诊断报告完成——现状调研和数据分析完成</t>
+          <t xml:space="preserve">  *  某型号 诊断报告完成——现状调研和数据分析完成</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M03 现状评估通过——推进委员会评审通过诊断报告</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  *  某型号 现状评估通过——推进委员会评审通过诊断报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -618,27 +650,29 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M04 精益体系发布——精益管理体系文件正式发布</t>
+          <t xml:space="preserve">  *  某型号 精益体系发布——精益管理体系文件正式发布</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M05 培训计划完成——全员理念培训和骨干技能培训完成</t>
+          <t xml:space="preserve">  *  某型号 培训计划完成——全员理念培训和骨干技能培训完成</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M06 体系评审通过——推进委员会确认体系文件和培训成果</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  *  某型号 体系评审通过——推进委员会确认体系文件和培训成果</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
@@ -646,27 +680,29 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M07 试点线选定——试点产线确定并完成现状分析</t>
+          <t xml:space="preserve">  *  某型号 试点线选定——试点产线确定并完成现状分析</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M08 试点线改善完成——试点线各改善项目实施完毕</t>
+          <t xml:space="preserve">  *  某型号 试点线改善完成——试点线各改善项目实施完毕</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M09 试点成果评审——试点成果达到预期目标并通过评审</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  *  某型号 试点成果评审——试点成果达到预期目标并通过评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
@@ -674,27 +710,29 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M10 推广计划发布——全面推广计划获得批准</t>
+          <t xml:space="preserve">  *  某型号 推广计划发布——全面推广计划获得批准</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M11 50%产线完成推广——一半产线完成精益改善</t>
+          <t xml:space="preserve">  *  某型号 50%产线完成推广——一半产线完成精益改善</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M12 100%产线完成推广——所有计划产线完成精益改善</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  *  某型号 100%产线完成推广——所有计划产线完成精益改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
@@ -702,20 +740,24 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M13 成熟度评估完成——精益成熟度评估达到目标等级</t>
+          <t xml:space="preserve">  *  某型号 成熟度评估完成——精益成熟度评估达到目标等级</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  M14 项目收尾——项目总结报告完成、经验归档</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  *  某型号 项目收尾——项目总结报告完成、经验归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
@@ -723,6 +765,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
@@ -730,6 +773,9 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
@@ -737,6 +783,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
@@ -744,6 +791,9 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -751,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
@@ -1005,7 +1056,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1062,7 +1113,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -1099,7 +1150,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1136,7 +1187,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -1173,7 +1224,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1210,7 +1261,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1247,7 +1298,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1284,7 +1335,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>M08</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -1321,7 +1372,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>M09</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1358,7 +1409,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1395,7 +1446,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1432,7 +1483,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -1469,7 +1520,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1506,7 +1557,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>M14</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
